--- a/backend/data/financials_by_company/1748.HK.xlsx
+++ b/backend/data/financials_by_company/1748.HK.xlsx
@@ -647,58 +647,58 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-634.617623</v>
+        <v>699.017909</v>
       </c>
       <c r="C2" t="n">
-        <v>0.010942</v>
+        <v>0.005777</v>
       </c>
       <c r="D2" t="n">
-        <v>24094000</v>
+        <v>15499000</v>
       </c>
       <c r="E2" t="n">
-        <v>-58000</v>
+        <v>121000</v>
       </c>
       <c r="F2" t="n">
-        <v>-58000</v>
+        <v>121000</v>
       </c>
       <c r="G2" t="n">
-        <v>8497000</v>
+        <v>1721000</v>
       </c>
       <c r="H2" t="n">
-        <v>10072000</v>
+        <v>10293000</v>
       </c>
       <c r="I2" t="n">
-        <v>41891000</v>
+        <v>44022000</v>
       </c>
       <c r="J2" t="n">
-        <v>24036000</v>
+        <v>15620000</v>
       </c>
       <c r="K2" t="n">
-        <v>13964000</v>
+        <v>5327000</v>
       </c>
       <c r="L2" t="n">
-        <v>-4777000</v>
+        <v>-3593000</v>
       </c>
       <c r="M2" t="n">
-        <v>5373000</v>
+        <v>3596000</v>
       </c>
       <c r="N2" t="n">
-        <v>596000</v>
+        <v>3000</v>
       </c>
       <c r="O2" t="n">
-        <v>8554365.382377001</v>
+        <v>1600699.017909</v>
       </c>
       <c r="P2" t="n">
-        <v>8497000</v>
+        <v>1721000</v>
       </c>
       <c r="Q2" t="n">
-        <v>46721000</v>
+        <v>48710000</v>
       </c>
       <c r="R2" t="n">
-        <v>13964000</v>
+        <v>5327000</v>
       </c>
       <c r="S2" t="n">
         <v>440000000</v>
@@ -707,77 +707,79 @@
         <v>440000000</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0193</v>
+        <v>0.0039</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0193</v>
+        <v>0.0039</v>
       </c>
       <c r="W2" t="n">
-        <v>8497000</v>
+        <v>1721000</v>
       </c>
       <c r="X2" t="n">
-        <v>8497000</v>
+        <v>1721000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>8497000</v>
+        <v>1721000</v>
       </c>
       <c r="AA2" t="n">
-        <v>8497000</v>
+        <v>1721000</v>
       </c>
       <c r="AB2" t="n">
-        <v>8497000</v>
+        <v>1721000</v>
       </c>
       <c r="AC2" t="n">
-        <v>94000</v>
+        <v>10000</v>
       </c>
       <c r="AD2" t="n">
-        <v>8591000</v>
+        <v>1731000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1358000</v>
+        <v>1165000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-3000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>-4777000</v>
+        <v>-3593000</v>
       </c>
       <c r="AI2" t="n">
-        <v>5373000</v>
+        <v>3596000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>596000</v>
+        <v>3000</v>
       </c>
       <c r="AK2" t="n">
-        <v>12195000</v>
+        <v>3621000</v>
       </c>
       <c r="AL2" t="n">
-        <v>4830000</v>
+        <v>4688000</v>
       </c>
       <c r="AM2" t="n">
-        <v>480000</v>
+        <v>1034000</v>
       </c>
       <c r="AN2" t="n">
-        <v>4350000</v>
+        <v>3664000</v>
       </c>
       <c r="AO2" t="n">
-        <v>4350000</v>
+        <v>3664000</v>
       </c>
       <c r="AP2" t="n">
-        <v>17025000</v>
+        <v>8309000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>41891000</v>
+        <v>44022000</v>
       </c>
       <c r="AR2" t="n">
-        <v>58916000</v>
+        <v>52331000</v>
       </c>
       <c r="AS2" t="n">
-        <v>58916000</v>
+        <v>52331000</v>
       </c>
     </row>
     <row r="3">
@@ -919,58 +921,58 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>699.017909</v>
+        <v>-634.617623</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005777</v>
+        <v>0.010942</v>
       </c>
       <c r="D4" t="n">
-        <v>15499000</v>
+        <v>24094000</v>
       </c>
       <c r="E4" t="n">
-        <v>121000</v>
+        <v>-58000</v>
       </c>
       <c r="F4" t="n">
-        <v>121000</v>
+        <v>-58000</v>
       </c>
       <c r="G4" t="n">
-        <v>1721000</v>
+        <v>8497000</v>
       </c>
       <c r="H4" t="n">
-        <v>10293000</v>
+        <v>10072000</v>
       </c>
       <c r="I4" t="n">
-        <v>44022000</v>
+        <v>41891000</v>
       </c>
       <c r="J4" t="n">
-        <v>15620000</v>
+        <v>24036000</v>
       </c>
       <c r="K4" t="n">
-        <v>5327000</v>
+        <v>13964000</v>
       </c>
       <c r="L4" t="n">
-        <v>-3593000</v>
+        <v>-4777000</v>
       </c>
       <c r="M4" t="n">
-        <v>3596000</v>
+        <v>5373000</v>
       </c>
       <c r="N4" t="n">
-        <v>3000</v>
+        <v>596000</v>
       </c>
       <c r="O4" t="n">
-        <v>1600699.017909</v>
+        <v>8554365.382377001</v>
       </c>
       <c r="P4" t="n">
-        <v>1721000</v>
+        <v>8497000</v>
       </c>
       <c r="Q4" t="n">
-        <v>48710000</v>
+        <v>46721000</v>
       </c>
       <c r="R4" t="n">
-        <v>5327000</v>
+        <v>13964000</v>
       </c>
       <c r="S4" t="n">
         <v>440000000</v>
@@ -979,79 +981,77 @@
         <v>440000000</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0039</v>
+        <v>0.0193</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0039</v>
+        <v>0.0193</v>
       </c>
       <c r="W4" t="n">
-        <v>1721000</v>
+        <v>8497000</v>
       </c>
       <c r="X4" t="n">
-        <v>1721000</v>
+        <v>8497000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1721000</v>
+        <v>8497000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1721000</v>
+        <v>8497000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1721000</v>
+        <v>8497000</v>
       </c>
       <c r="AC4" t="n">
-        <v>10000</v>
+        <v>94000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1731000</v>
+        <v>8591000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1165000</v>
+        <v>1358000</v>
       </c>
       <c r="AF4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-3000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>-3593000</v>
+        <v>-4777000</v>
       </c>
       <c r="AI4" t="n">
-        <v>3596000</v>
+        <v>5373000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3000</v>
+        <v>596000</v>
       </c>
       <c r="AK4" t="n">
-        <v>3621000</v>
+        <v>12195000</v>
       </c>
       <c r="AL4" t="n">
-        <v>4688000</v>
+        <v>4830000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1034000</v>
+        <v>480000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3664000</v>
+        <v>4350000</v>
       </c>
       <c r="AO4" t="n">
-        <v>3664000</v>
+        <v>4350000</v>
       </c>
       <c r="AP4" t="n">
-        <v>8309000</v>
+        <v>17025000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>44022000</v>
+        <v>41891000</v>
       </c>
       <c r="AR4" t="n">
-        <v>52331000</v>
+        <v>58916000</v>
       </c>
       <c r="AS4" t="n">
-        <v>52331000</v>
+        <v>58916000</v>
       </c>
     </row>
   </sheetData>
@@ -1322,11 +1322,9 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>440000000</v>
       </c>
@@ -1334,40 +1332,40 @@
         <v>440000000</v>
       </c>
       <c r="E2" t="n">
-        <v>36725000</v>
+        <v>38939000</v>
       </c>
       <c r="F2" t="n">
-        <v>58871000</v>
+        <v>72131000</v>
       </c>
       <c r="G2" t="n">
-        <v>124367000</v>
+        <v>121030000</v>
       </c>
       <c r="H2" t="n">
-        <v>182592000</v>
+        <v>161708000</v>
       </c>
       <c r="I2" t="n">
-        <v>10121000</v>
+        <v>-32345000</v>
       </c>
       <c r="J2" t="n">
-        <v>124367000</v>
+        <v>121030000</v>
       </c>
       <c r="K2" t="n">
-        <v>646000</v>
+        <v>31453000</v>
       </c>
       <c r="L2" t="n">
-        <v>124367000</v>
+        <v>121030000</v>
       </c>
       <c r="M2" t="n">
-        <v>171690000</v>
+        <v>144650000</v>
       </c>
       <c r="N2" t="n">
-        <v>124367000</v>
+        <v>121030000</v>
       </c>
       <c r="O2" t="n">
-        <v>124367000</v>
+        <v>121030000</v>
       </c>
       <c r="P2" t="n">
-        <v>35031000</v>
+        <v>31630000</v>
       </c>
       <c r="Q2" t="n">
         <v>74892000</v>
@@ -1379,98 +1377,100 @@
         <v>4400000</v>
       </c>
       <c r="T2" t="n">
-        <v>63356000</v>
+        <v>79469000</v>
       </c>
       <c r="U2" t="n">
-        <v>47784000</v>
+        <v>37952000</v>
       </c>
       <c r="V2" t="n">
-        <v>47784000</v>
+        <v>37952000</v>
       </c>
       <c r="W2" t="n">
-        <v>461000</v>
+        <v>14332000</v>
       </c>
       <c r="X2" t="n">
-        <v>47323000</v>
+        <v>23620000</v>
       </c>
       <c r="Y2" t="n">
-        <v>15572000</v>
+        <v>41517000</v>
       </c>
       <c r="Z2" t="n">
-        <v>11087000</v>
+        <v>34179000</v>
       </c>
       <c r="AA2" t="n">
-        <v>185000</v>
+        <v>17121000</v>
       </c>
       <c r="AB2" t="n">
-        <v>10902000</v>
+        <v>17058000</v>
       </c>
       <c r="AC2" t="n">
-        <v>2823000</v>
+        <v>6834000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1242000</v>
+        <v>936000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1581000</v>
+        <v>5898000</v>
       </c>
       <c r="AF2" t="n">
-        <v>187723000</v>
+        <v>200499000</v>
       </c>
       <c r="AG2" t="n">
-        <v>162030000</v>
+        <v>191327000</v>
       </c>
       <c r="AH2" t="n">
-        <v>162030000</v>
+        <v>191327000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-65983000</v>
+        <v>-23908000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>228013000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>215235000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>191327000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>227309000</v>
+        <v>214946000</v>
       </c>
       <c r="AM2" t="n">
-        <v>704000</v>
+        <v>289000</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>25693000</v>
+        <v>9172000</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1244000</v>
+        <v>3506000</v>
       </c>
       <c r="AR2" t="n">
-        <v>812000</v>
+        <v>314000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1651000</v>
+        <v>2165000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1651000</v>
+        <v>2165000</v>
       </c>
       <c r="AU2" t="n">
-        <v>153000</v>
+        <v>149000</v>
       </c>
       <c r="AV2" t="n">
-        <v>333000</v>
+        <v>1299000</v>
       </c>
       <c r="AW2" t="n">
-        <v>21500000</v>
+        <v>1739000</v>
       </c>
       <c r="AX2" t="n">
-        <v>21500000</v>
+        <v>1739000</v>
       </c>
       <c r="AY2" t="n">
-        <v>21500000</v>
+        <v>1739000</v>
       </c>
     </row>
     <row r="3">
@@ -1628,9 +1628,11 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
         <v>440000000</v>
       </c>
@@ -1638,40 +1640,40 @@
         <v>440000000</v>
       </c>
       <c r="E4" t="n">
-        <v>38939000</v>
+        <v>36725000</v>
       </c>
       <c r="F4" t="n">
-        <v>72131000</v>
+        <v>58871000</v>
       </c>
       <c r="G4" t="n">
-        <v>121030000</v>
+        <v>124367000</v>
       </c>
       <c r="H4" t="n">
-        <v>161708000</v>
+        <v>182592000</v>
       </c>
       <c r="I4" t="n">
-        <v>-32345000</v>
+        <v>10121000</v>
       </c>
       <c r="J4" t="n">
-        <v>121030000</v>
+        <v>124367000</v>
       </c>
       <c r="K4" t="n">
-        <v>31453000</v>
+        <v>646000</v>
       </c>
       <c r="L4" t="n">
-        <v>121030000</v>
+        <v>124367000</v>
       </c>
       <c r="M4" t="n">
-        <v>144650000</v>
+        <v>171690000</v>
       </c>
       <c r="N4" t="n">
-        <v>121030000</v>
+        <v>124367000</v>
       </c>
       <c r="O4" t="n">
-        <v>121030000</v>
+        <v>124367000</v>
       </c>
       <c r="P4" t="n">
-        <v>31630000</v>
+        <v>35031000</v>
       </c>
       <c r="Q4" t="n">
         <v>74892000</v>
@@ -1683,100 +1685,98 @@
         <v>4400000</v>
       </c>
       <c r="T4" t="n">
-        <v>79469000</v>
+        <v>63356000</v>
       </c>
       <c r="U4" t="n">
-        <v>37952000</v>
+        <v>47784000</v>
       </c>
       <c r="V4" t="n">
-        <v>37952000</v>
+        <v>47784000</v>
       </c>
       <c r="W4" t="n">
-        <v>14332000</v>
+        <v>461000</v>
       </c>
       <c r="X4" t="n">
-        <v>23620000</v>
+        <v>47323000</v>
       </c>
       <c r="Y4" t="n">
-        <v>41517000</v>
+        <v>15572000</v>
       </c>
       <c r="Z4" t="n">
-        <v>34179000</v>
+        <v>11087000</v>
       </c>
       <c r="AA4" t="n">
-        <v>17121000</v>
+        <v>185000</v>
       </c>
       <c r="AB4" t="n">
-        <v>17058000</v>
+        <v>10902000</v>
       </c>
       <c r="AC4" t="n">
-        <v>6834000</v>
+        <v>2823000</v>
       </c>
       <c r="AD4" t="n">
-        <v>936000</v>
+        <v>1242000</v>
       </c>
       <c r="AE4" t="n">
-        <v>5898000</v>
+        <v>1581000</v>
       </c>
       <c r="AF4" t="n">
-        <v>200499000</v>
+        <v>187723000</v>
       </c>
       <c r="AG4" t="n">
-        <v>191327000</v>
+        <v>162030000</v>
       </c>
       <c r="AH4" t="n">
-        <v>191327000</v>
+        <v>162030000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-23908000</v>
+        <v>-65983000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>215235000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>191327000</v>
-      </c>
+        <v>228013000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>214946000</v>
+        <v>227309000</v>
       </c>
       <c r="AM4" t="n">
-        <v>289000</v>
+        <v>704000</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>9172000</v>
+        <v>25693000</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3506000</v>
+        <v>1244000</v>
       </c>
       <c r="AR4" t="n">
-        <v>314000</v>
+        <v>812000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2165000</v>
+        <v>1651000</v>
       </c>
       <c r="AT4" t="n">
-        <v>2165000</v>
+        <v>1651000</v>
       </c>
       <c r="AU4" t="n">
-        <v>149000</v>
+        <v>153000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1299000</v>
+        <v>333000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1739000</v>
+        <v>21500000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1739000</v>
+        <v>21500000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1739000</v>
+        <v>21500000</v>
       </c>
     </row>
   </sheetData>
@@ -2007,121 +2007,129 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>15045000</v>
+        <v>11893000</v>
       </c>
       <c r="C2" t="n">
-        <v>-14192000</v>
+        <v>-16503000</v>
       </c>
       <c r="D2" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>13900000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
       <c r="F2" t="n">
-        <v>-2172000</v>
+        <v>-2763000</v>
       </c>
       <c r="G2" t="n">
-        <v>21500000</v>
+        <v>1739000</v>
       </c>
       <c r="H2" t="n">
-        <v>32549000</v>
+        <v>5881000</v>
       </c>
       <c r="I2" t="n">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="J2" t="n">
-        <v>-11068000</v>
+        <v>-4144000</v>
       </c>
       <c r="K2" t="n">
-        <v>-32634000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-16027000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-16027000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-16826000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
       <c r="P2" t="n">
-        <v>-2192000</v>
+        <v>-2603000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2192000</v>
+        <v>-2603000</v>
       </c>
       <c r="R2" t="n">
-        <v>-14192000</v>
+        <v>-16503000</v>
       </c>
       <c r="S2" t="n">
-        <v>12000000</v>
+        <v>13900000</v>
       </c>
       <c r="T2" t="n">
-        <v>4349000</v>
+        <v>-1974000</v>
       </c>
       <c r="U2" t="n">
-        <v>5925000</v>
+        <v>786000</v>
       </c>
       <c r="V2" t="n">
-        <v>596000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
       <c r="Y2" t="n">
-        <v>-2172000</v>
+        <v>-2763000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-2172000</v>
+        <v>-2763000</v>
       </c>
       <c r="AB2" t="n">
-        <v>17217000</v>
+        <v>14656000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-94000</v>
+        <v>-10000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-5128000</v>
+        <v>-3578000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1067000</v>
+        <v>3001000</v>
       </c>
       <c r="AF2" t="n">
-        <v>130000</v>
+        <v>-275000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1195000</v>
+        <v>3632000</v>
       </c>
       <c r="AH2" t="n">
-        <v>126000</v>
+        <v>-756000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-128000</v>
+        <v>400000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4777000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>3593000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
       <c r="AL2" t="n">
-        <v>10072000</v>
+        <v>10293000</v>
       </c>
       <c r="AM2" t="n">
-        <v>10072000</v>
+        <v>10293000</v>
       </c>
       <c r="AN2" t="n">
-        <v>58000</v>
+        <v>-118000</v>
       </c>
       <c r="AO2" t="n">
-        <v>8000</v>
+        <v>-253000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8591000</v>
+        <v>1731000</v>
       </c>
     </row>
     <row r="3">
@@ -2243,129 +2251,121 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>11893000</v>
+        <v>15045000</v>
       </c>
       <c r="C4" t="n">
-        <v>-16503000</v>
+        <v>-14192000</v>
       </c>
       <c r="D4" t="n">
-        <v>13900000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>12000000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-2763000</v>
+        <v>-2172000</v>
       </c>
       <c r="G4" t="n">
-        <v>1739000</v>
+        <v>21500000</v>
       </c>
       <c r="H4" t="n">
-        <v>5881000</v>
+        <v>32549000</v>
       </c>
       <c r="I4" t="n">
-        <v>2000</v>
+        <v>19000</v>
       </c>
       <c r="J4" t="n">
-        <v>-4144000</v>
+        <v>-11068000</v>
       </c>
       <c r="K4" t="n">
-        <v>-16826000</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
+        <v>-32634000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-16027000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-16027000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-2603000</v>
+        <v>-2192000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2603000</v>
+        <v>-2192000</v>
       </c>
       <c r="R4" t="n">
-        <v>-16503000</v>
+        <v>-14192000</v>
       </c>
       <c r="S4" t="n">
-        <v>13900000</v>
+        <v>12000000</v>
       </c>
       <c r="T4" t="n">
-        <v>-1974000</v>
+        <v>4349000</v>
       </c>
       <c r="U4" t="n">
-        <v>786000</v>
+        <v>5925000</v>
       </c>
       <c r="V4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
+        <v>596000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>-2763000</v>
+        <v>-2172000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2763000</v>
+        <v>-2172000</v>
       </c>
       <c r="AB4" t="n">
-        <v>14656000</v>
+        <v>17217000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-10000</v>
+        <v>-94000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3578000</v>
+        <v>-5128000</v>
       </c>
       <c r="AE4" t="n">
-        <v>3001000</v>
+        <v>-1067000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-275000</v>
+        <v>130000</v>
       </c>
       <c r="AG4" t="n">
-        <v>3632000</v>
+        <v>-1195000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-756000</v>
+        <v>126000</v>
       </c>
       <c r="AI4" t="n">
-        <v>400000</v>
+        <v>-128000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3593000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
+        <v>4777000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>10293000</v>
+        <v>10072000</v>
       </c>
       <c r="AM4" t="n">
-        <v>10293000</v>
+        <v>10072000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-118000</v>
+        <v>58000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-253000</v>
+        <v>8000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1731000</v>
+        <v>8591000</v>
       </c>
     </row>
   </sheetData>
@@ -2900,187 +2900,187 @@
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
         </is>
       </c>
       <c r="EK1" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Jiagan  Chen', 'age': 50, 'title': 'Chairman of the Board', 'yearBorn': 1975, 'fiscalYear': 2023, 'totalPay': 1951518, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wenjun  Xu', 'age': 68, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1957, 'fiscalYear': 2023, 'totalPay': 1661533, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shifeng  Lin', 'age': 47, 'title': 'Financial Controller &amp; Executive Director', 'yearBorn': 1978, 'fiscalYear': 2023, 'totalPay': 1214800, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ming  Chen', 'age': 28, 'title': 'Executive Director', 'yearBorn': 1997, 'fiscalYear': 2023, 'totalPay': 916978, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yanbiao  Chen', 'age': 49, 'title': 'Executive Director', 'yearBorn': 1976, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Weipeng  Liu', 'age': 55, 'title': 'Executive Director', 'yearBorn': 1970, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Dunyu  Liu', 'age': 62, 'title': 'Executive Director', 'yearBorn': 1963, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Mei Ka  Lui', 'age': 40, 'title': 'Company Secretary', 'yearBorn': 1985, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Jiagan  Chen', 'age': 50, 'title': 'Chairman of the Board', 'yearBorn': 1975, 'fiscalYear': 2023, 'totalPay': 1951441, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wenjun  Xu', 'age': 68, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1957, 'fiscalYear': 2023, 'totalPay': 1661468, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shifeng  Lin', 'age': 47, 'title': 'Financial Controller &amp; Executive Director', 'yearBorn': 1978, 'fiscalYear': 2023, 'totalPay': 1214753, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ming  Chen', 'age': 28, 'title': 'Executive Director', 'yearBorn': 1997, 'fiscalYear': 2023, 'totalPay': 916942, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yanbiao  Chen', 'age': 49, 'title': 'Executive Director', 'yearBorn': 1976, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Weipeng  Liu', 'age': 55, 'title': 'Executive Director', 'yearBorn': 1970, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Dunyu  Liu', 'age': 62, 'title': 'Executive Director', 'yearBorn': 1963, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Mei Ka  Lui', 'age': 40, 'title': 'Company Secretary', 'yearBorn': 1985, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -3203,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.173</v>
+        <v>1.038</v>
       </c>
       <c r="AD2" t="n">
         <v>7.3333335</v>
@@ -3298,10 +3298,10 @@
         <v>440000000</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.4058242</v>
+        <v>2.4057298</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.731558</v>
+        <v>0.73158675</v>
       </c>
       <c r="BJ2" t="n">
         <v>1703980800</v>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BT2" t="n">
         <v>0.285</v>
@@ -3447,122 +3447,122 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DA2" t="b">
-        <v>0</v>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>XIN YUAN ENT</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="DB2" t="n">
+        <v>1740036204</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>finmb_579749581</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>13.54839</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="n">
         <v>1537925400000</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="DO2" t="n">
         <v>0.21000004</v>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>Xin Yuan Enterprises Group Limited</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>1.5 - 1.77</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>Xin Yuan Enterprises Group Limited</t>
-        </is>
-      </c>
-      <c r="DG2" t="n">
-        <v>13.54839</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DJ2" t="n">
-        <v>1740036204</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>finmb_579749581</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DQ2" t="b">
-        <v>0</v>
-      </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>XIN YUAN ENT</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
           <t>HKSE</t>
         </is>
       </c>
+      <c r="DS2" t="n">
+        <v>0</v>
+      </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="DV2" t="n">
         <v>0.17333333</v>
       </c>
-      <c r="DW2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>1.5 - 1.77</t>
         </is>
       </c>
+      <c r="DW2" t="n">
+        <v>-0.00999999</v>
+      </c>
       <c r="DX2" t="n">
-        <v>-0.00999999</v>
+        <v>-0.0056497124</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0.0056497124</v>
+        <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0</v>
+        <v>1724755274</v>
       </c>
       <c r="EA2" t="n">
         <v>1724755274</v>
       </c>
-      <c r="EB2" t="n">
-        <v>1724755274</v>
-      </c>
-      <c r="EC2" t="b">
-        <v>0</v>
+      <c r="EB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.24</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
         <v>0</v>
@@ -3574,13 +3574,13 @@
         <v>0</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="EI2" t="n">
         <v>15</v>
       </c>
-      <c r="EJ2" t="n">
-        <v>15</v>
+      <c r="EJ2" t="b">
+        <v>0</v>
       </c>
       <c r="EK2" t="inlineStr"/>
     </row>
